--- a/www/download/IND.gdp.s.du.rpA2.xlsx
+++ b/www/download/IND.gdp.s.du.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77601.2963005123</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78347.2405326098</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78741.9982235756</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79961.5404874868</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84675.7557643655</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88021.8910285225</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86081.7738377933</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89953.0781196547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99491.0380160072</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108914.474600541</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120022.844705371</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128877.830137162</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148563.571066669</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174944.197276805</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170567.707445224</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39357.954900067</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39640.6653877578</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39645.9761961352</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39575.7897523456</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41502.0355660029</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42230.3934637285</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41578.1920063223</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42357.5206634151</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44799.5391930634</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51223.4224752532</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53558.6538558033</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55500.0682859687</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62537.9377778839</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69813.4418480492</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61654.8532435759</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27568.9209984434</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27579.081484161</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27540.2497467636</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27606.1819578746</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28872.177835669</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30046.8358120284</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29421.6076652858</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29564.6995818328</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31640.3931534227</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35060.4393372264</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37489.5890940798</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39621.2914175593</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45258.9284331775</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52056.5041752607</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47481.3153358806</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29182.174718094</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29514.9061649442</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27613.1713466139</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25067.7695236703</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24764.0337661071</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23559.6594044694</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21935.5397660993</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22021.4101133229</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24416.4916225858</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28168.1572023944</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30712.840785991</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33069.317035045</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38242.2100685798</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42216.6073697994</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38742.2193197514</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>612928.381951027</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>603834.848648193</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>613176.524749872</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>606009.548177548</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>658386.950005693</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>685789.722159793</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>670628.416488916</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>705283.400436611</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>777993.382487165</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>902770.03895177</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>994622.610324746</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1075612.16251379</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>1272146.22816357</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>1467741.53498129</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>1371163.6747467</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145061.916633357</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147007.638421288</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147818.699453547</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147603.432731656</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154337.180422254</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159763.153192625</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>152916.830076441</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156228.408969072</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169766.493249453</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>189314.280059939</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204489.406347046</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217047.671098491</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248189.949099627</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272872.953545953</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>247140.038584283</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5.603</t>
+          <t>5602592.71553491</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.691</t>
+          <t>5691294.89675747</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.679</t>
+          <t>5679426.08559061</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>5619806.86076482</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.898</t>
+          <t>5898110.24121423</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6.024</t>
+          <t>6024145.01865546</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.949</t>
+          <t>5948881.61579116</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6.184</t>
+          <t>6184279.57351099</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6.806</t>
+          <t>6806435.75092529</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7.565</t>
+          <t>7565255.69316053</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8259770.83009813</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9.086</t>
+          <t>9085885.80699995</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>10.438</t>
+          <t>10438114.8467956</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11.956</t>
+          <t>11955538.3208878</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>11.175</t>
+          <t>11175293.8489</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3174.68049973904</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3149.37143015146</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3026.77513065092</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2907.98042109006</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3002.7853951419</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3104.77172874135</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3083.50837058916</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3160.55714281787</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3488.83202023301</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3781.17004078133</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4075.79267437081</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4344.59552442646</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5232.28486941917</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5713.27130372386</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5285.13644581294</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75231.6497427382</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75938.3561544508</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74267.37686041</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72058.8751896379</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72011.2585789715</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71851.3972209305</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66965.2785194822</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67180.566000597</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70672.8186658055</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>77798.6068963622</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84761.007640331</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89828.7679954218</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101942.780485437</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114553.921390041</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101737.89851043</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>412789.072454636</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>397093.10281528</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384248.683699003</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>392268.505876131</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>399842.534928399</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>398464.654351489</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>380323.507574583</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>380781.104942649</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>413039.578600048</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456185.373197423</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>471550.977078345</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>485573.68534775</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552044.313623887</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>608739.929270972</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>557551.341923293</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29940.5846424663</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29925.7904269252</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30414.8336803129</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31026.7459874682</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32634.371689843</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33257.5674385673</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32439.9175167127</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33025.4577845763</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35353.1916248247</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38365.5135647049</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41615.1148277926</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44308.5845483727</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47247.0878264729</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54020.8155997354</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48806.7103837883</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122286.814982121</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128546.876964378</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132689.025414026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139194.704675592</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151823.641121051</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164608.770615363</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164685.014415394</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173834.415928151</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>191937.988920771</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215306.675396272</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241754.821638055</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261592.281137038</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299721.895368263</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>321648.480057722</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278148.142673382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11594.7353558663</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11114.9914166791</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10679.42851374</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10047.4565900066</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9527.76373451705</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9382.56019140209</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9354.0603680476</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9463.52568990061</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10485.1555814563</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11921.0316473355</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12777.9737008286</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14051.7613974971</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16001.5730926237</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17114.6480883448</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13771.2321621697</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30012.2264971241</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30369.1126349915</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31005.0761084902</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31012.204432722</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32766.9315969231</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33069.0614539856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32275.3818970541</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32945.8265413057</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34965.9939728597</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38730.5160301772</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41635.7565132466</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44151.1127517571</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50689.0309298939</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56102.7804962191</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50682.4679191073</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212039.745868389</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214414.247151933</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212455.745725291</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212409.80217606</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>223648.076601467</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>223625.599275379</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218422.450809977</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218249.520270941</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232821.310627615</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>257703.207216028</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>277989.124700974</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292324.359393951</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>343449.170222699</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>384816.138527507</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350255.991167311</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267711.810289933</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268704.9869622</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275797.851189132</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279214.749280606</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292832.108969777</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>298925.440941119</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>290208.67547315</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>298409.927067422</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>319074.443694584</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>346606.788838609</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>373868.005056474</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>393669.47043545</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>445143.636143441</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>483057.709418271</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>447975.637716325</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40400.5976600683</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40283.8368068354</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39010.7265448182</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40609.9403432044</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43084.1040744749</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43550.4408238593</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41841.2368897133</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42753.6294533794</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45756.2708466277</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52603.1759390028</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55433.4969657395</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61972.5945672903</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>70698.4876912798</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76354.7177749542</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71614.9189973366</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61180.9587468182</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60553.242334151</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59421.1138219418</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59944.4218842523</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64753.6305012027</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64046.9321091467</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60037.2055823132</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61424.9189937171</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65579.2249002847</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71794.4813234708</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74571.229895746</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78576.1954954536</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87610.6519531861</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91563.8665000027</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85856.2009525312</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>517124.178292462</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>531885.566438738</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516752.034148428</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>530882.109025375</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>596332.735103477</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>644619.373628494</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>626833.349415052</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>663652.035631768</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>731541.095881882</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>815670.733404373</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>778007.596359622</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>767802.975840475</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>886102.434268265</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>973476.10247544</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>920233.053812546</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4.706</t>
+          <t>4706381.22178299</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.895</t>
+          <t>4895157.06605926</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4.908</t>
+          <t>4907637.4970674</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.921</t>
+          <t>4921308.53943885</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.065</t>
+          <t>5064918.25776728</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5.423</t>
+          <t>5422544.32666875</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.534</t>
+          <t>5534406.33483606</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5.617</t>
+          <t>5617486.55446459</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6.419</t>
+          <t>6419121.10069114</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>7239900.00282812</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7.931</t>
+          <t>7931044.61649067</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.323</t>
+          <t>8322739.47652015</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>9.128</t>
+          <t>9128222.90696687</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10050195.6207482</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>9340471.13771792</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16991.0201637106</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18095.2784197678</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18386.5127676131</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19324.9804419858</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21261.2576545628</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22326.5482960189</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22238.4331679564</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23236.7923106998</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25772.7388774672</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29329.1067525361</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33123.440429492</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36777.9734273753</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42759.1318579785</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48836.3477004692</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43194.1108637666</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170786.328369199</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>173903.506288731</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>175187.322777866</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180121.473741634</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>189748.486745507</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>191669.462382245</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182917.032849518</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187310.823919342</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205358.688726894</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225958.974085414</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247634.588596055</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265744.576682516</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304375.154844382</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>339973.071649516</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302562.368912875</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>832119.143911919</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>837929.917429277</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>827308.734268327</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>796846.532387312</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810701.977507947</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>821278.730255562</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>789074.702561017</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>783425.481074982</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>845475.164310668</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>918702.640226192</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>964016.640654745</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1009300.70892011</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1133506.32563501</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1.197</t>
+          <t>1196777.00727118</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>1024195.49502359</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>413188.733194232</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>411401.558901229</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>408244.439412787</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>387603.849994624</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>411945.196363465</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436337.486238678</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>425697.067962276</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>442659.290786126</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>485001.956850702</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>553079.197260428</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>566769.316337187</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>591072.273122041</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>647452.659069953</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>711592.923680785</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>655746.748348447</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24058.4199887696</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23932.5420318964</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22788.6549673777</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23059.7296315208</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22250.3818598445</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23354.4042381825</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21558.3349719059</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21723.5731306023</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23966.1397770761</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26200.7466272596</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29920.6018379749</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30738.2821259568</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36597.4180111103</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>40419.2857587968</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34439.6941941949</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1692.43745808169</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1706.13905842251</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1751.26563531682</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1809.25030467509</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1901.66580062288</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2024.71675684283</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2015.89830472831</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2117.64580375792</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2189.53623968242</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2776.90020868383</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3058.57207185546</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3164.11673909346</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3711.68343945264</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4348.68514070302</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4633.6975907739</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12999.0099324707</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12783.1278868663</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12549.3962202226</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11930.9211587379</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11582.1734766073</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10828.5835794025</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10175.3404863904</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10085.9439526485</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10943.8070619967</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12155.9534430479</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12828.8905419411</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14011.9798725102</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16067.4725650429</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17464.1263872324</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12433.1654779459</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>395687.122769995</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>414253.625229296</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423943.093874988</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>429779.232109208</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>456637.756155731</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>471680.824199663</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>463596.227084851</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>475351.593983945</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>524065.279839791</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>601389.812449038</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>667672.730527741</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>696204.352158228</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>787031.621742149</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>926279.896561224</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>841013.388337989</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1086.98154363151</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1080.76869271216</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1034.45447571861</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1004.1665543423</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1055.1095364361</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1079.94516849042</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>908.700876220005</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1080.43287771508</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1129.43127081794</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1317.81498129741</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1371.37399304459</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1444.25154756081</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1609.36120258134</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1746.04852233074</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1649.94698906739</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56599.7630068915</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58104.7300637057</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59316.4616278486</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59633.2344354955</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64687.4372215153</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62555.4414776797</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61948.7359175847</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64994.775510035</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72422.8344844967</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80841.7028460492</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86038.2963945116</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90300.0925332165</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102764.426382448</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>114894.400523828</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106315.141853978</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225134.338189787</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227089.060881696</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225088.729574429</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222164.320830219</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221911.150575807</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217734.487049145</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>190797.762105857</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187364.612185869</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203975.162751136</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226873.058242662</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>248440.230968451</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267635.112178856</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>308076.43422059</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>351802.856120461</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>322752.818845542</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33742.7605606433</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33715.5957908021</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32454.2423696967</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31594.8662603278</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33404.4239625784</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34597.6161304952</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33706.8396192633</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34187.0122004934</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36561.2500496487</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41183.4935354815</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43586.1157800806</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47206.5889711589</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53587.2334950974</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59059.6291867203</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54613.2617645745</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88572.6621036034</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89237.6655099733</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81151.8192416026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76166.5663247051</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92227.8116933028</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91578.9200334266</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87956.9220614255</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82488.118337865</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89209.4594311383</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94988.3165790773</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100871.242442139</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106466.289213186</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120538.750440644</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134774.866208726</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>124777.524864478</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1298387.32354065</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.261</t>
+          <t>1260982.54896813</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>1185543.04828111</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114230.57469449</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>1155828.62260346</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>1179184.5476576</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.142</t>
+          <t>1142347.14990466</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.161</t>
+          <t>1161396.35892823</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1250036.71322917</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.364</t>
+          <t>1364044.1414478</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1449620.76856911</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.511</t>
+          <t>1511331.19237906</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.705</t>
+          <t>1704868.0833957</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.859</t>
+          <t>1858594.51592529</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>1662792.38786654</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31516.9339629052</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30387.6253982497</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29480.4574632551</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28247.8981134842</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27970.8754612427</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27492.5160206785</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26346.8709781178</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25451.6588239393</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26645.7151134492</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29955.5987475983</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32249.9535994165</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33273.6181592595</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38425.2427553137</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43899.8810712481</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39357.2744135594</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12626.2186356788</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12156.0842781236</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11751.5002184983</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11491.7464780939</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12045.8230235851</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12452.8667339004</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11539.4801083123</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11831.1631184474</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12940.4317627765</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14265.3567330299</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15296.6207929045</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16201.7568121444</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18578.1296875997</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21545.4136535989</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19585.4941112136</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48096.9678219437</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>48013.7400552431</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47036.2540632629</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47200.8322649097</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50280.0350607231</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54230.9635109837</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53534.7130819243</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54347.2957329748</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57794.9305885841</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63828.612441924</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68535.0660691982</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72165.3719618794</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>84061.9160882237</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93962.2612594818</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83960.0049298858</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184475.414437707</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194499.597681306</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194794.341827437</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186871.849327706</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192667.159142925</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>184567.523678258</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179178.556189885</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181242.160084095</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195443.019489659</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>211811.131831484</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>236917.205880429</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241927.974060132</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264808.326630918</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>298480.15473054</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271188.039038211</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>116390.256155665</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117462.323029687</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>120910.793016211</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>121390.670226194</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128048.395231056</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133473.933985738</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123080.82876179</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127690.730467554</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140220.959420782</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>158136.640245075</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>174657.828018384</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186206.530135183</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216583.476071785</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242925.452337021</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>221557.479270187</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>1300626.89422955</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1317345.60765021</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>1321978.39610545</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>1349343.23876183</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>1404855.31605717</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1447874.67264405</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>1381721.17149305</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>1375851.17356572</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1455302.49922254</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>1621614.36025288</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1743484.30093618</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.867</t>
+          <t>1866789.31420579</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.113</t>
+          <t>2112509.45668382</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.285</t>
+          <t>2285142.77605003</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>2021499.07589168</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>11.778</t>
+          <t>11777580.3251009</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>12.139</t>
+          <t>12138918.3362634</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12.272</t>
+          <t>12272139.797989</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12.341</t>
+          <t>12340563.1523873</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12999572.2613256</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>13.832</t>
+          <t>13831668.0012158</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13.973</t>
+          <t>13973322.968032</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>14.721</t>
+          <t>14720853.2810752</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>16.637</t>
+          <t>16636845.1978497</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>19.021</t>
+          <t>19020643.2156679</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>20.792</t>
+          <t>20792493.527963</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>22.623</t>
+          <t>22622680.9314783</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>26.047</t>
+          <t>26047193.1847039</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>29.878</t>
+          <t>29877725.0640038</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>28.445</t>
+          <t>28444713.8804135</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30.067</t>
+          <t>30066520.6929297</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30.727</t>
+          <t>30727355.2045012</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.764</t>
+          <t>30764208.5893888</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.709</t>
+          <t>30708896.2451452</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>32.188</t>
+          <t>32188409.8910965</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>33.723</t>
+          <t>33722599.7614167</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>33.596</t>
+          <t>33595983.6338188</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>34.807</t>
+          <t>34806746.049177</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>38.83</t>
+          <t>38829681.0110233</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>43.806</t>
+          <t>43806170.5567152</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>47.608</t>
+          <t>47608339.6011572</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>51.207</t>
+          <t>51207193.2951265</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>58.332</t>
+          <t>58332265.4137705</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>65.943</t>
+          <t>65942786.2254791</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>61.677</t>
+          <t>61677414.5269594</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
